--- a/docs/jp/01_要件定義書.xlsx
+++ b/docs/jp/01_要件定義書.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>iTMS 株式会社 御中</t>
+          <t>統合G</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>(担当部門)</t>
+          <t>張　泊江</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>(担当部門)</t>
+          <t>張　泊江</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1161,163 +1161,135 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>出典: METHODOLOGY.md Purpose + Compliance framing。</t>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>1.2 本書の目的</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>1.2 本納品物の目的</t>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>本書は、SDTM 知識ベース (SDTM Knowledge Base) が満たすべき要件を定義する。具体的には、業務要件 (§2)、機能要件 (§3)、非機能要件 (§4)、制約条件 (§5)、および前提条件 (§6) を体系的に記述し、iTMS 株式会社が本知識ベースの設計根拠・品質基準・利用上の前提を理解できるよう提示することを目的とする。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>本納品物 (要件定義書、基本設計書、運用保守マニュアル、テスト結果報告書、詳細設計書、トレーサビリティ管理表、進捗報告書、用語集) は、本知識ベースおよびその検証根拠資料を、iTMS 株式会社が自社業務に違和感なく組み込めるよう、日本職場の標準ドキュメント形式 (Excel 主体) に再構成したものである。</t>
+          <t>本知識ベースの設計・構成の詳細は 02 基本設計書に、日常運用手順は 03 運用保守マニュアルに、検証結果は 04 テスト結果報告書にそれぞれ委譲する。本書はこれら後続文書の共通根拠章であり、後続文書は本書の各節を引用して設計・運用・試験の根拠とする。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Excel 形式を主体に選定した理由は、受信者側の社内文書レビュー、印刷、承認欄記入といった既存業務手順との適合性が高いためである。</t>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>1.3 想定読者</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>出典: docs/jp/PLAN.md §0.1。</t>
+          <t>本書の想定読者は、IT 分野および医療データ分野の双方に知見を有する実務担当者である。具体的には、臨床試験データ管理、SDTM データプログラミング、マッピング品質確認、SDTM 教育に従事する技術者および管理者を想定する。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>1.3 想定読者</t>
+          <t>1.4 関連文書一覧</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>本納品物の想定読者は、IT 分野および医療データ分野の双方に知見を有する実務担当者である。具体的には、臨床試験データ管理、SDTM データプログラミング、マッピング品質確認、SDTM 教育に従事する技術者および管理者を想定する。</t>
+          <t>本書に関連する納品文書一覧は以下のとおりである。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>出典: docs/jp/PLAN.md §0 受信者欄。</t>
+          <t>・02 基本設計書: 本書の機能要件 (FR-01〜FR-11) および非機能要件 (NFR-01〜NFR-06) を実現する基本設計を提示する。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>1.4 関連文書一覧</t>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>・03 運用保守マニュアル: 本書の非機能要件 (NFR-04) および制約条件 (§5) に基づく日常運用手順・保守手順を記述する。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>本納品物は以下の文書群で構成される。</t>
+          <t>・04 テスト結果報告書: 本書の前提条件 (§6) に基づき試験範囲を画定し、実施結果・合格判定・根拠資料を記録する。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>・02 基本設計書: 知識ベース全体構成、データモデル、外部 IF を定義する設計根拠章。</t>
+          <t>・05 詳細設計書: 02 基本設計書の各章の詳細展開。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>・03 運用保守マニュアル: 日常運用手順、保守作業手順、障害対応の運用根拠章。</t>
+          <t>・06 トレーサビリティ管理表: 本書の要件・設計・試験・根拠資料の横断対応表。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>・04 テスト結果報告書: 試験範囲、実施結果、合格判定、根拠資料一覧の検証根拠章。</t>
+          <t>・07 進捗報告書: 全体サマリ・工程別進捗・課題管理・今後の予定。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>・01 要件定義書: 本書。背景、業務要件、機能要件、非機能要件、制約条件、前提条件の最上位根拠章。</t>
+          <t>・99 用語集: 英語・日本語・中国語・出典規格の四列対照辞書。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>・05 詳細設計書: 02 基本設計の章別詳細展開。</t>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>1.5 本書の位置付け</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>・06 トレーサビリティ管理表: 要件、設計、試験、根拠資料の横断対応表。</t>
+          <t>本書は、SDTM 知識ベースの要件を定義する最上位根拠文書である。後続三文書はそれぞれ本書の各節を引用して設計・運用・試験の根拠とする。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>・07 進捗報告書: 全体サマリ、工程別進捗、課題管理、今後の予定。</t>
+          <t>・02 基本設計書は、本書 §3 機能要件 (FR-01〜FR-11) および §4 非機能要件 (NFR-01〜NFR-06) を実現する基本設計を提示する。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>・99 用語集: 英語、日本語、中国語、出典規格の四列対照辞書。</t>
+          <t>・03 運用保守マニュアルは、本書 §4 非機能要件および §5 制約条件に基づく運用手順を定める。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>出典: docs/jp/PLAN.md §1。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>1.5 本書の位置付け</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>本書は本納品物の最上位根拠章であり、後段三文書 (02 基本設計書、03 運用保守マニュアル、04 テスト結果報告書) すべての根拠章となる。01 は本書 §3 機能要件を、02 は本書 §4 非機能要件および §5 制約条件を、03 は本書 §6 前提条件を引用して試験範囲を画定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>出典: docs/jp/PLAN.md §1 v0.3 改訂注記。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>出典: METHODOLOGY.md Purpose + Compliance framing / docs/jp/PLAN.md §0 §1。</t>
+          <t>・04 テスト結果報告書は、本書 §6 前提条件に従い試験範囲を画定する。</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1395,100 +1367,79 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>出典: METHODOLOGY.md §6 first bullet。</t>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>2.2 一次資料との対応関係</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>2.2 一次資料との対応関係</t>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>本知識ベースは、CDISC が公表する以下四種の公式刊行物のみを根拠とする。第三者要約や言換え版から派生したコンテンツを一切含まない。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>本知識ベースは、CDISC が公表する以下四種の公式刊行物のみを根拠とする。第三者要約や言換え版から派生したコンテンツを一切含まない。</t>
+          <t>・SDTM 実装ガイド (SDTMIG: SDTM Implementation Guide) PDF v3.4 (2021 年 11 月 29 日公表)、461 頁。各ドメインの仕様、業務上の前提、実装例を収録する。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>・SDTM 実装ガイド (SDTMIG: SDTM Implementation Guide) PDF v3.4 (2021 年 11 月 29 日公表)、461 頁。各ドメインの仕様、業務上の前提、実装例を収録する。</t>
+          <t>・SDTM モデル (SDTM Model) PDF v2.0 Final (2021 年 11 月 29 日公表)、74 頁。観察クラスおよび変数役割の概念モデルを規定する。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>・SDTM モデル (SDTM Model) PDF v2.0 Final (2021 年 11 月 29 日公表)、74 頁。観察クラスおよび変数役割の概念モデルを規定する。</t>
+          <t>・SDTMIG xlsx v3.4。63 ドメインにわたる 1,917 変数の構造化メタデータを含む。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>・SDTMIG xlsx v3.4。63 ドメインにわたる 1,917 変数の構造化メタデータを含む。</t>
+          <t>・CDISC 受控用語 (Controlled Terminology) xlsx 2024 年版。1,005 のコードリスト、合計 37,939 用語を含む。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>・CDISC 受控用語 (Controlled Terminology) xlsx 2024 年版。1,005 のコードリスト、合計 37,939 用語を含む。</t>
+          <t>原刊行物自体は本リポジトリに再配布せず、CDISC が著作権を保持する。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>原刊行物自体は本リポジトリに再配布せず、CDISC が著作権を保持する。</t>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>2.3 業務的限界</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>出典: METHODOLOGY.md §1 Table。</t>
+          <t>本知識ベースは作業参照資料としての性質を有し、以下二点の業務的限界を本書冒頭で明示する。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>2.3 業務的限界</t>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>第一に、本知識ベースは、米国 21 CFR Part 11 または PMDA が想定する電子記録および電子署名要件を充足する電磁的記録の代替ではない。組織標準作業手順書がこれら電子記録について規定する場合、その規定が優先される。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>本知識ベースは作業参照資料としての性質を有し、以下二点の業務的限界を本書冒頭で明示する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>第一に、本知識ベースは、米国 21 CFR Part 11 または PMDA が想定する電子記録および電子署名要件を充足する電磁的記録の代替ではない。組織標準作業手順書がこれら電子記録について規定する場合、その規定が優先される。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="18" t="inlineStr">
-        <is>
           <t>第二に、規制当局への提出時の権威源は CDISC 公式刊行物であり、本知識ベースの記述と公式刊行物との間に差異が見られた場合は、公式刊行物が優先される。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>出典: METHODOLOGY.md §6 (last 2 bullets)。</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1528,7 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 PDF を入力とし、ページ位置を機械的に索引化する。視覚推定値の混入を排除し、page_index.json を唯一の権威源とする。</t>
+          <t>SDTMIG v3.4 PDF を入力とし、ページ位置を機械的に索引化する。視覚的推定値を排除し、機械処理による精確なページ索引を唯一の参照源とする。</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1759,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>合格判定基準は定量化する。覆盖率は 95% 以上、占位マーカー (待補全、TODO、待後続) は 0 件、行頁比は概ね 1 頁あたり 15 行から 20 行を基準とする。「見た目で正しい」といった主観評価は許容しない。</t>
+          <t>合格判定基準は定量化する。原典資料に対する覆盖率は 95% 以上、未記入・未確定マーカーは 0 件とする。主観的評価のみによる合格判定は許容しない。</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -1830,7 +1781,7 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>ファイルを作成した処理プロセスまたは担当者は、当該ファイルを承認できない。承認担当者は出典 PDF を独立に読み、構造化された覆盖率報告を作成する。</t>
+          <t>コンテンツを作成した担当者は、当該コンテンツを承認できない。承認担当者は出典 PDF を独立に参照し、構造化された確認報告を作成する。</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
@@ -2063,7 +2014,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>本納品物の機密区分は公開可レベルとする。CDISC 規格自体が公開資料であり、本納品物にも個人情報および組織機密情報を含めない。</t>
+          <t>本知識ベースおよび関連納品文書の機密区分は公開可レベルとする。CDISC 規格自体が公開資料であり、これらに個人情報および組織機密情報を含めない。</t>
         </is>
       </c>
     </row>
